--- a/accountant-skill/data/Jan2026/general_journal.xlsx
+++ b/accountant-skill/data/Jan2026/general_journal.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="General Journal" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="General Journal" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -515,10 +515,10 @@
         </is>
       </c>
       <c r="D2" s="3" t="n">
-        <v>5010</v>
+        <v>50000</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>1200</v>
+        <v>12000</v>
       </c>
       <c r="F2" s="3" t="n">
         <v>450000</v>
@@ -554,7 +554,7 @@
         </is>
       </c>
       <c r="D3" s="3" t="n">
-        <v>5700</v>
+        <v>65000</v>
       </c>
       <c r="E3" s="3" t="n">
         <v>1320</v>
@@ -593,10 +593,10 @@
         </is>
       </c>
       <c r="D4" s="3" t="n">
-        <v>1110</v>
+        <v>11000</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>1100</v>
+        <v>11000</v>
       </c>
       <c r="F4" s="3" t="n">
         <v>15000</v>
@@ -628,10 +628,10 @@
         </is>
       </c>
       <c r="D5" s="3" t="n">
-        <v>5920</v>
+        <v>65000</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>1020</v>
+        <v>10100</v>
       </c>
       <c r="F5" s="3" t="n">
         <v>8500</v>
@@ -667,10 +667,10 @@
         </is>
       </c>
       <c r="D6" s="3" t="n">
-        <v>5410</v>
+        <v>65000</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>5900</v>
+        <v>68000</v>
       </c>
       <c r="F6" s="3" t="n">
         <v>12000</v>

--- a/accountant-skill/data/Jan2026/general_journal.xlsx
+++ b/accountant-skill/data/Jan2026/general_journal.xlsx
@@ -437,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I6"/>
+  <dimension ref="A1:I18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -689,6 +689,470 @@
         </is>
       </c>
     </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>JV-006</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>Opening WIP balance from Dec2025</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="n">
+        <v>50300</v>
+      </c>
+      <c r="E7" s="2" t="n">
+        <v>12400</v>
+      </c>
+      <c r="F7" s="3" t="n">
+        <v>50000</v>
+      </c>
+      <c r="G7" s="3" t="n">
+        <v>50000</v>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>PC99</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>2026-01-15</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>JV-007</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>Direct materials issued to production</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="n">
+        <v>50320</v>
+      </c>
+      <c r="E8" s="2" t="n">
+        <v>50010</v>
+      </c>
+      <c r="F8" s="3" t="n">
+        <v>120000</v>
+      </c>
+      <c r="G8" s="3" t="n">
+        <v>120000</v>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>PC01</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>CC101</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>2026-01-15</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>JV-007</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>Direct materials issued to production</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="n">
+        <v>50320</v>
+      </c>
+      <c r="E9" s="2" t="n">
+        <v>50110</v>
+      </c>
+      <c r="F9" s="3" t="n">
+        <v>30000</v>
+      </c>
+      <c r="G9" s="3" t="n">
+        <v>30000</v>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>PC01</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>CC105</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>2026-01-31</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>JV-008</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>Direct labor allocated to WIP</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="n">
+        <v>50330</v>
+      </c>
+      <c r="E10" s="2" t="n">
+        <v>53000</v>
+      </c>
+      <c r="F10" s="3" t="n">
+        <v>80000</v>
+      </c>
+      <c r="G10" s="3" t="n">
+        <v>80000</v>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>PC01</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>CC101</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>2026-01-31</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>JV-009</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>Manufacturing overhead applied to WIP</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="n">
+        <v>50340</v>
+      </c>
+      <c r="E11" s="2" t="n">
+        <v>53100</v>
+      </c>
+      <c r="F11" s="3" t="n">
+        <v>15000</v>
+      </c>
+      <c r="G11" s="3" t="n">
+        <v>15000</v>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>PC99</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>CC201</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>2026-01-31</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>JV-009</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>Manufacturing overhead applied to WIP</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="n">
+        <v>50340</v>
+      </c>
+      <c r="E12" s="2" t="n">
+        <v>53200</v>
+      </c>
+      <c r="F12" s="3" t="n">
+        <v>20000</v>
+      </c>
+      <c r="G12" s="3" t="n">
+        <v>20000</v>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>PC99</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>CC201</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>2026-01-31</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>JV-009</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>Manufacturing overhead applied to WIP</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="n">
+        <v>50340</v>
+      </c>
+      <c r="E13" s="2" t="n">
+        <v>53300</v>
+      </c>
+      <c r="F13" s="3" t="n">
+        <v>10000</v>
+      </c>
+      <c r="G13" s="3" t="n">
+        <v>10000</v>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>PC99</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>CC201</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>2026-01-31</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>JV-010</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>Clear WIP - transfer to Finished Goods</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="n">
+        <v>50350</v>
+      </c>
+      <c r="E14" s="2" t="n">
+        <v>50300</v>
+      </c>
+      <c r="F14" s="3" t="n">
+        <v>50000</v>
+      </c>
+      <c r="G14" s="3" t="n">
+        <v>50000</v>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>PC01</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>CC105</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>2026-01-31</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>JV-010</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>Clear WIP - transfer to Finished Goods</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="n">
+        <v>50350</v>
+      </c>
+      <c r="E15" s="2" t="n">
+        <v>50320</v>
+      </c>
+      <c r="F15" s="3" t="n">
+        <v>150000</v>
+      </c>
+      <c r="G15" s="3" t="n">
+        <v>150000</v>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>PC01</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>CC105</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>2026-01-31</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>JV-010</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>Clear WIP - transfer to Finished Goods</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="n">
+        <v>50350</v>
+      </c>
+      <c r="E16" s="2" t="n">
+        <v>50330</v>
+      </c>
+      <c r="F16" s="3" t="n">
+        <v>80000</v>
+      </c>
+      <c r="G16" s="3" t="n">
+        <v>80000</v>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>PC01</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>CC105</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>2026-01-31</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>JV-010</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>Clear WIP - transfer to Finished Goods</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="n">
+        <v>50350</v>
+      </c>
+      <c r="E17" s="2" t="n">
+        <v>50340</v>
+      </c>
+      <c r="F17" s="3" t="n">
+        <v>45000</v>
+      </c>
+      <c r="G17" s="3" t="n">
+        <v>45000</v>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>PC01</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>CC105</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>2026-01-31</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>JV-011</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>Record closing WIP per physical count</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="n">
+        <v>12400</v>
+      </c>
+      <c r="E18" s="2" t="n">
+        <v>50310</v>
+      </c>
+      <c r="F18" s="3" t="n">
+        <v>65000</v>
+      </c>
+      <c r="G18" s="3" t="n">
+        <v>65000</v>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>PC01</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>CC105</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
